--- a/output/laminas_comunales/comunal_p_basica_a_2019_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_p_basica_a_2019_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,82 +384,1882 @@
         </is>
       </c>
       <c r="C2">
-        <v>54.5918350219727</v>
+        <v>107380.84375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C3">
-        <v>35.3260879516602</v>
+        <v>106776.5625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C4">
-        <v>20.2127666473389</v>
+        <v>101652.875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C5">
-        <v>19.1280364990234</v>
+        <v>100033.109375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C6">
-        <v>18.125</v>
+        <v>96045.4375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>94389.625</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>91777.484375</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>91049.921875</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>88767.390625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>88378.9921875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>87925.5546875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>85490.6953125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Iquique</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C14">
+        <v>85458.7890625</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>84822.59375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>84514.3125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>84027.203125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>82490.6328125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>81888.9296875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>81668.328125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>81487.90625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>79940.703125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>78278.8359375</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>77851.6171875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>77479.8046875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>77432.3046875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>77050.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>76258.390625</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>75988.796875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>75555.890625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>75171.453125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>72875.1796875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>72794.4453125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>70507.6484375</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>69227.3359375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>65762.4609375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>65449.4921875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>65420.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>64297.26171875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>62188.69140625</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>61058.5703125</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>60459.8984375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>55903.19140625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>76.92308044433589</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>64.7058792114258</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>61.1111106872559</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>57.471263885498</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>54.5918350219727</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>54.2205581665039</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>53.5412712097168</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>52.8446769714355</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>52.183406829834</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>52.0833320617676</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>50.630916595459</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>49.4137344360351</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>49.0797538757324</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>49.0445861816406</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>48.7603302001953</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>48.6301383972168</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>48.1003036499023</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>47.3118286132812</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>47.0097351074219</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>46.413501739502</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>46.2962951660156</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>46.09375</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>45.9882583618164</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>45.783130645752</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>45.4545440673828</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>45.1612892150879</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>44.8275871276855</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>44.680850982666</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>44.0217399597168</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>43.6781616210938</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>43.6170196533203</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>43.389591217041</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>43.2989692687988</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>42.6632347106934</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>42.5531921386719</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>42.375</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>41.0653877258301</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>40.8602142333984</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>40.6091384887695</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>40.4541168212891</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>39.6119499206543</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>38.7012977600098</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>38.2978706359863</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>37.037036895752</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>36.6935501098633</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>35.3260879516602</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>35.2125434875488</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>35.0624618530273</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>33.673469543457</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>32.9113922119141</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>29.6482410430908</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>29.4117641448975</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>28.2845478057861</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>27.9569892883301</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>27.8350524902344</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>27.2727279663086</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>26.6242046356201</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>24.6575336456299</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>23.5807857513428</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>23.3502540588379</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>21.264368057251</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>21.2048187255859</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>20.2127666473389</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>19.4444446563721</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>19.1280364990234</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>18.4615383148193</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>18.125</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>17.791410446167</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>17.7033500671387</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>16.7633609771729</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>16.3190536499023</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>14.8051948547363</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>12.9990539550781</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>12.8548898696899</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>12.7545051574707</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>12.378303527832</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C122">
         <v>12.1890306472778</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>12.1330728530884</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>10.0806455612183</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>9.73822021484375</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>8.851737022399901</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>6.68007612228394</v>
       </c>
     </row>
   </sheetData>
